--- a/output/daily_ratings/uk_ratings_2026-03-21.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-03-21.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:P142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,14 +501,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.072727272727272</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Mount Ruapehu (IRE)</t>
+          <t>Alther Walden (HUN)</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K2" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>75.43000000000001</v>
+        <v>161.09</v>
       </c>
       <c r="N2" t="n">
-        <v>60.3</v>
+        <v>76.7</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -553,20 +553,20 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>6.072727272727272</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -579,33 +579,33 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tuscan Point (IRE)</t>
+          <t>Rastnet (IRE)</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="n">
-        <v>75.43000000000001</v>
+        <v>161.09</v>
       </c>
       <c r="N3" t="n">
-        <v>64.8</v>
+        <v>75.2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -613,20 +613,20 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>6.072727272727272</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -639,33 +639,33 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Moonhall Lass (IRE)</t>
+          <t>Selenic (IRE)</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="K4" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="L4" t="n">
-        <v>0.65</v>
+        <v>4.5</v>
       </c>
       <c r="M4" t="n">
-        <v>75.43000000000001</v>
+        <v>161.09</v>
       </c>
       <c r="N4" t="n">
-        <v>46.1</v>
+        <v>66.8</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -673,20 +673,20 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>6.072727272727272</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -699,33 +699,33 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bullington Bry</t>
+          <t>Cabrera (IRE)</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="K5" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>75.43000000000001</v>
+        <v>161.09</v>
       </c>
       <c r="N5" t="n">
-        <v>57.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>6.072727272727272</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -759,33 +759,33 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ardaddy</t>
+          <t>Leagle Aid (IRE)</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K6" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>9.5</v>
       </c>
       <c r="M6" t="n">
-        <v>75.43000000000001</v>
+        <v>161.09</v>
       </c>
       <c r="N6" t="n">
-        <v>50.1</v>
+        <v>59.8</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -799,14 +799,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>6.072727272727272</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -819,33 +819,33 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Amerjeet</t>
+          <t>Machete (FR)</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="K7" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="L7" t="n">
-        <v>2.08</v>
+        <v>12</v>
       </c>
       <c r="M7" t="n">
-        <v>75.43000000000001</v>
+        <v>161.09</v>
       </c>
       <c r="N7" t="n">
-        <v>52.7</v>
+        <v>57.5</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -853,20 +853,20 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>6.072727272727272</v>
+        <v>12.44545454545455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -879,37 +879,37 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Up The Monk</t>
+          <t>Charlies Choice</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K8" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="L8" t="n">
-        <v>3.58</v>
+        <v>23</v>
       </c>
       <c r="M8" t="n">
-        <v>75.43000000000001</v>
+        <v>161.09</v>
       </c>
       <c r="N8" t="n">
-        <v>40.1</v>
+        <v>44.3</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -919,14 +919,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -939,31 +939,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mr Fustic (IRE)</t>
+          <t>Wareeth (IRE)</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
         <v>133</v>
       </c>
       <c r="K9" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>102.74</v>
+        <v>99.2</v>
       </c>
       <c r="N9" t="n">
-        <v>53.2</v>
+        <v>89.8</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -977,14 +977,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -997,33 +997,33 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Showcasing Star (IRE)</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>133</v>
       </c>
       <c r="K10" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>102.74</v>
+        <v>99.2</v>
       </c>
       <c r="N10" t="n">
-        <v>52</v>
+        <v>55.4</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1037,14 +1037,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1057,37 +1057,37 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Heretic (IRE)</t>
+          <t>Balmoral Boy (IRE)</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K11" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>23</v>
       </c>
       <c r="M11" t="n">
-        <v>102.74</v>
+        <v>99.2</v>
       </c>
       <c r="N11" t="n">
-        <v>50.8</v>
+        <v>37.5</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1097,14 +1097,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1117,37 +1117,37 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Scenario</t>
+          <t>Haltonwood (IRE)</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>23.75</v>
       </c>
       <c r="M12" t="n">
-        <v>102.74</v>
+        <v>99.2</v>
       </c>
       <c r="N12" t="n">
-        <v>44.4</v>
+        <v>36.8</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1157,14 +1157,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1177,37 +1177,37 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Trais Fluors</t>
+          <t>Thunder Rush</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K13" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5.25</v>
+        <v>25</v>
       </c>
       <c r="M13" t="n">
-        <v>102.74</v>
+        <v>99.2</v>
       </c>
       <c r="N13" t="n">
-        <v>40.9</v>
+        <v>34.4</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1217,14 +1217,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1237,54 +1237,54 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ribston Pippin (IRE)</t>
+          <t>The Bitters</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K14" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>9</v>
+        <v>31.5</v>
       </c>
       <c r="M14" t="n">
-        <v>102.74</v>
+        <v>99.2</v>
       </c>
       <c r="N14" t="n">
-        <v>31.9</v>
+        <v>16.7</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1297,54 +1297,54 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Dinah Myte</t>
+          <t>The Floors Munky</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K15" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>9.1</v>
+        <v>35.5</v>
       </c>
       <c r="M15" t="n">
-        <v>102.74</v>
+        <v>99.2</v>
       </c>
       <c r="N15" t="n">
-        <v>29.8</v>
+        <v>22.1</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1357,54 +1357,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
-      </c>
-      <c r="G16" t="n">
-        <v>8</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Conquest Of Power</t>
+          <t>Starglow (IRE)</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="K16" t="n">
-        <v>47</v>
-      </c>
-      <c r="L16" t="n">
-        <v>9.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>102.74</v>
-      </c>
-      <c r="N16" t="n">
-        <v>24.9</v>
-      </c>
+        <v>99.2</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>8.059090909090909</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1417,33 +1409,31 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fifty Sent</t>
+          <t>Recency Bias (IRE)</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K17" t="n">
-        <v>55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>12.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>102.74</v>
+        <v>87.84</v>
       </c>
       <c r="N17" t="n">
-        <v>23.3</v>
+        <v>64.2</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1457,53 +1447,53 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="n">
         <v>2</v>
       </c>
-      <c r="C18" t="n">
-        <v>8.059090909090909</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>All Weather</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" t="n">
-        <v>10</v>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Create (IRE)</t>
+          <t>Zatsgood</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K18" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>102.74</v>
+        <v>87.84</v>
       </c>
       <c r="N18" t="n">
-        <v>6.6</v>
+        <v>48.4</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1517,14 +1507,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>8.059090909090909</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1537,54 +1527,54 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Coverbridge</t>
+          <t>Billyjoegold</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K19" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="M19" t="n">
-        <v>102.74</v>
+        <v>87.84</v>
       </c>
       <c r="N19" t="n">
-        <v>-12.7</v>
+        <v>26.8</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>8.059090909090909</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1600,28 +1590,30 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Timber Twelve</t>
+          <t>Pop The Question</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>11.6</v>
+      </c>
       <c r="M20" t="n">
-        <v>102.29</v>
+        <v>87.84</v>
       </c>
       <c r="N20" t="n">
-        <v>59.6</v>
+        <v>22</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1629,20 +1621,20 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>8.059090909090909</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1658,30 +1650,30 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Clatford (IRE)</t>
+          <t>Finally Escaped</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>11.65</v>
       </c>
       <c r="M21" t="n">
-        <v>102.29</v>
+        <v>87.84</v>
       </c>
       <c r="N21" t="n">
-        <v>49.7</v>
+        <v>23.3</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1695,14 +1687,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>8.059090909090909</v>
+        <v>7.063636363636363</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1718,51 +1710,51 @@
         <v>4</v>
       </c>
       <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Porters Song</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>133</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="M22" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="N22" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
         <v>3</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Saint Of The Sea</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>123</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M22" t="n">
-        <v>102.29</v>
-      </c>
-      <c r="N22" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1775,33 +1767,31 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Flash Kozo (IRE)</t>
+          <t>Smartanck (IRE)</t>
         </is>
       </c>
       <c r="I23" t="n">
         <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.4</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>102.29</v>
+        <v>101.94</v>
       </c>
       <c r="N23" t="n">
-        <v>48.7</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1809,20 +1799,20 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1835,33 +1825,33 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Floating Market</t>
+          <t>Kameko Fever (IRE)</t>
         </is>
       </c>
       <c r="I24" t="n">
         <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="L24" t="n">
-        <v>4.15</v>
+        <v>0.15</v>
       </c>
       <c r="M24" t="n">
-        <v>102.29</v>
+        <v>101.94</v>
       </c>
       <c r="N24" t="n">
-        <v>39</v>
+        <v>63.6</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1875,53 +1865,53 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8.022727272727273</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="n">
         <v>3</v>
       </c>
-      <c r="C25" t="n">
-        <v>8.059090909090909</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>All Weather</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6</v>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Cobalt Comet</t>
+          <t>Sailor Batt (IRE)</t>
         </is>
       </c>
       <c r="I25" t="n">
         <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="L25" t="n">
-        <v>7.15</v>
+        <v>0.2</v>
       </c>
       <c r="M25" t="n">
-        <v>102.29</v>
+        <v>101.94</v>
       </c>
       <c r="N25" t="n">
-        <v>34.3</v>
+        <v>62.1</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1935,14 +1925,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1955,33 +1945,33 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Love Fresh</t>
+          <t>Zoustellar (IRE)</t>
         </is>
       </c>
       <c r="I26" t="n">
         <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="L26" t="n">
-        <v>13.65</v>
+        <v>0.7</v>
       </c>
       <c r="M26" t="n">
-        <v>102.29</v>
+        <v>101.94</v>
       </c>
       <c r="N26" t="n">
-        <v>11.9</v>
+        <v>55.5</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1989,20 +1979,20 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2015,33 +2005,33 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Luscious Lil</t>
+          <t>Space Moon (IRE)</t>
         </is>
       </c>
       <c r="I27" t="n">
         <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="L27" t="n">
-        <v>17.4</v>
+        <v>0.75</v>
       </c>
       <c r="M27" t="n">
-        <v>102.29</v>
+        <v>101.94</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>55.8</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2055,74 +2045,74 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>8.022727272727273</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Norcross Brow</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" t="n">
-        <v>8.059090909090909</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>All Weather</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" t="n">
-        <v>9</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>August Spring</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>4</v>
-      </c>
       <c r="J28" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L28" t="n">
-        <v>107.4</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>102.29</v>
+        <v>101.94</v>
       </c>
       <c r="N28" t="n">
-        <v>-21.1</v>
+        <v>58.6</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2135,31 +2125,33 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Welbury</t>
+          <t>Kingofthecarnival (FR)</t>
         </is>
       </c>
       <c r="I29" t="n">
         <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3.25</v>
+      </c>
       <c r="M29" t="n">
-        <v>103.15</v>
+        <v>101.94</v>
       </c>
       <c r="N29" t="n">
-        <v>41.6</v>
+        <v>54</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2173,14 +2165,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2193,33 +2185,33 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tommos Ginjaninja</t>
+          <t>Secret Testimony</t>
         </is>
       </c>
       <c r="I30" t="n">
         <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K30" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>5.25</v>
       </c>
       <c r="M30" t="n">
-        <v>103.15</v>
+        <v>101.94</v>
       </c>
       <c r="N30" t="n">
-        <v>36.1</v>
+        <v>45.2</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2227,20 +2219,20 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2253,14 +2245,14 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tough Date (IRE)</t>
+          <t>Captain Bruce (IRE)</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2270,37 +2262,37 @@
         <v>125</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L31" t="n">
-        <v>2.75</v>
+        <v>29.25</v>
       </c>
       <c r="M31" t="n">
-        <v>103.15</v>
+        <v>101.94</v>
       </c>
       <c r="N31" t="n">
-        <v>36.6</v>
+        <v>-22.6</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2313,33 +2305,31 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Portman Blue</t>
+          <t>Barrys Boy (IRE)</t>
         </is>
       </c>
       <c r="I32" t="n">
         <v>4</v>
       </c>
       <c r="J32" t="n">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="K32" t="n">
-        <v>72</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6.5</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>103.15</v>
+        <v>102.94</v>
       </c>
       <c r="N32" t="n">
-        <v>34.8</v>
+        <v>35.7</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2347,20 +2337,20 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2373,33 +2363,33 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Lorton Valley</t>
+          <t>Selection (IRE)</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L33" t="n">
-        <v>9.75</v>
+        <v>0.15</v>
       </c>
       <c r="M33" t="n">
-        <v>103.15</v>
+        <v>102.94</v>
       </c>
       <c r="N33" t="n">
-        <v>19</v>
+        <v>44.9</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2407,20 +2397,20 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2433,33 +2423,33 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Filly Eilish (IRE)</t>
+          <t>Alpha Capture (IRE)</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L34" t="n">
-        <v>11</v>
+        <v>1.15</v>
       </c>
       <c r="M34" t="n">
-        <v>103.15</v>
+        <v>102.94</v>
       </c>
       <c r="N34" t="n">
-        <v>7.9</v>
+        <v>43.1</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2473,14 +2463,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2493,33 +2483,33 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Alembic</t>
+          <t>Criminal Shore (IRE)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="L35" t="n">
-        <v>15</v>
+        <v>1.2</v>
       </c>
       <c r="M35" t="n">
-        <v>103.15</v>
+        <v>102.94</v>
       </c>
       <c r="N35" t="n">
-        <v>3.9</v>
+        <v>43.2</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2527,20 +2517,20 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2553,33 +2543,33 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Rocklaw</t>
+          <t>Boubyan (IRE)</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L36" t="n">
-        <v>15.5</v>
+        <v>1.3</v>
       </c>
       <c r="M36" t="n">
-        <v>103.15</v>
+        <v>102.94</v>
       </c>
       <c r="N36" t="n">
-        <v>-5.8</v>
+        <v>35.1</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2587,20 +2577,20 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>8.059090909090909</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2613,54 +2603,54 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sweetstevie</t>
+          <t>Concert Boy (IRE)</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L37" t="n">
-        <v>22.5</v>
+        <v>1.8</v>
       </c>
       <c r="M37" t="n">
-        <v>103.15</v>
+        <v>102.94</v>
       </c>
       <c r="N37" t="n">
-        <v>-5.8</v>
+        <v>28.7</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>7.063636363636363</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2673,50 +2663,54 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Baandee</t>
+          <t>Harswell Ruby (IRE)</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K38" t="n">
-        <v>75</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3.55</v>
+      </c>
       <c r="M38" t="n">
-        <v>91.06</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
+        <v>102.94</v>
+      </c>
+      <c r="N38" t="n">
+        <v>32.4</v>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>7.063636363636363</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2729,31 +2723,33 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tenzi (IRE)</t>
+          <t>Tasever</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K39" t="n">
-        <v>68</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4.55</v>
+      </c>
       <c r="M39" t="n">
-        <v>91.06</v>
+        <v>102.94</v>
       </c>
       <c r="N39" t="n">
-        <v>15.8</v>
+        <v>28.8</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2761,20 +2757,20 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>7.063636363636363</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2787,54 +2783,54 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Irish Incentive (IRE)</t>
+          <t>Mr Nugget</t>
         </is>
       </c>
       <c r="I40" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>134</v>
+      </c>
+      <c r="K40" t="n">
+        <v>74</v>
+      </c>
+      <c r="L40" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="M40" t="n">
+        <v>102.94</v>
+      </c>
+      <c r="N40" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
         <v>3</v>
-      </c>
-      <c r="J40" t="n">
-        <v>128</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M40" t="n">
-        <v>91.06</v>
-      </c>
-      <c r="N40" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P40" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>7.063636363636363</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2847,33 +2843,33 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Wadirumm (IRE)</t>
+          <t>Hostelry</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J41" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="L41" t="n">
-        <v>3.35</v>
+        <v>5.65</v>
       </c>
       <c r="M41" t="n">
-        <v>91.06</v>
+        <v>102.94</v>
       </c>
       <c r="N41" t="n">
-        <v>9.6</v>
+        <v>17.8</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2887,14 +2883,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>5</v>
       </c>
       <c r="C42" t="n">
-        <v>7.063636363636363</v>
+        <v>8.022727272727273</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2907,33 +2903,33 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Ndoto</t>
+          <t>Lessay (IRE)</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L42" t="n">
-        <v>6.85</v>
+        <v>5.8</v>
       </c>
       <c r="M42" t="n">
-        <v>91.06</v>
+        <v>102.94</v>
       </c>
       <c r="N42" t="n">
-        <v>-3.7</v>
+        <v>15.7</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -2947,14 +2943,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" t="n">
-        <v>7.063636363636363</v>
+        <v>6</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2967,33 +2963,31 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Curtain Caller</t>
+          <t>Alfa Duplicate (IRE)</t>
         </is>
       </c>
       <c r="I43" t="n">
         <v>3</v>
       </c>
       <c r="J43" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>8.6</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>91.06</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>-9.699999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3007,14 +3001,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>6</v>
       </c>
       <c r="C44" t="n">
-        <v>4.972727272727273</v>
+        <v>6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3027,31 +3021,33 @@
         </is>
       </c>
       <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
         <v>2</v>
       </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fahrenheit Seven</t>
+          <t>Cool Molly (IRE)</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K44" t="n">
-        <v>99</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M44" t="n">
-        <v>57.48</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>86.5</v>
+        <v>72</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3065,14 +3061,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>6</v>
       </c>
       <c r="C45" t="n">
-        <v>4.972727272727273</v>
+        <v>6</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3085,33 +3081,33 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Clearpoint</t>
+          <t>Espona Bay (IRE)</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K45" t="n">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>2.35</v>
       </c>
       <c r="M45" t="n">
-        <v>57.48</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>80.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3119,20 +3115,20 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>6</v>
       </c>
       <c r="C46" t="n">
-        <v>4.972727272727273</v>
+        <v>6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3145,33 +3141,33 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Liverpool Star (IRE)</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
         <v>3</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Against The Wind</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>4</v>
-      </c>
       <c r="J46" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K46" t="n">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="L46" t="n">
-        <v>1.5</v>
+        <v>4.35</v>
       </c>
       <c r="M46" t="n">
-        <v>57.48</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>82.7</v>
+        <v>57.2</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3179,20 +3175,20 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>6</v>
       </c>
       <c r="C47" t="n">
-        <v>4.972727272727273</v>
+        <v>6</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3205,33 +3201,33 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Rhythm N Hooves</t>
+          <t>Henriette Ronner</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="K47" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="L47" t="n">
-        <v>2.25</v>
+        <v>7.85</v>
       </c>
       <c r="M47" t="n">
-        <v>57.48</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>70.09999999999999</v>
+        <v>43</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3239,20 +3235,20 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>6</v>
       </c>
       <c r="C48" t="n">
-        <v>4.972727272727273</v>
+        <v>6</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3265,33 +3261,33 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kylian (IRE)</t>
+          <t>Pivotal Terms</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K48" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="L48" t="n">
-        <v>2.75</v>
+        <v>11.6</v>
       </c>
       <c r="M48" t="n">
-        <v>57.48</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>80.40000000000001</v>
+        <v>23.3</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3299,20 +3295,20 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>6</v>
       </c>
       <c r="C49" t="n">
-        <v>4.972727272727273</v>
+        <v>6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3325,33 +3321,33 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Gaeli (ITY)</t>
+          <t>Evolve</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K49" t="n">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="L49" t="n">
-        <v>2.9</v>
+        <v>16.35</v>
       </c>
       <c r="M49" t="n">
-        <v>57.48</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>80.09999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3359,20 +3355,20 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>6</v>
       </c>
       <c r="C50" t="n">
-        <v>4.972727272727273</v>
+        <v>6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3385,54 +3381,54 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Miss Attitude</t>
+          <t>Soul Warrior (IRE)</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K50" t="n">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="L50" t="n">
-        <v>3.4</v>
+        <v>21.85</v>
       </c>
       <c r="M50" t="n">
-        <v>57.48</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>78.2</v>
+        <v>-7.6</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C51" t="n">
-        <v>4.972727272727273</v>
+        <v>6</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3445,54 +3441,50 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Spartan Arrow (IRE)</t>
+          <t>Homestrait (IRE)</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K51" t="n">
-        <v>103</v>
-      </c>
-      <c r="L51" t="n">
-        <v>3.5</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>57.48</v>
-      </c>
-      <c r="N51" t="n">
-        <v>77</v>
-      </c>
+        <v>73.69</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C52" t="n">
-        <v>4.972727272727273</v>
+        <v>6</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3505,33 +3497,31 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G52" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Ziggys Triton (IRE)</t>
+          <t>Southern Warrior (IRE)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="K52" t="n">
-        <v>89</v>
-      </c>
-      <c r="L52" t="n">
-        <v>7.75</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>57.48</v>
+        <v>73.69</v>
       </c>
       <c r="N52" t="n">
-        <v>49.6</v>
+        <v>65.3</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3545,14 +3535,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C53" t="n">
-        <v>4.972727272727273</v>
+        <v>6</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3565,33 +3555,33 @@
         </is>
       </c>
       <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="n">
         <v>2</v>
       </c>
-      <c r="G53" t="n">
-        <v>10</v>
-      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Vintage Clarets</t>
+          <t>Mighty Vega (IRE)</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="K53" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="L53" t="n">
-        <v>12.75</v>
+        <v>0.15</v>
       </c>
       <c r="M53" t="n">
-        <v>57.48</v>
+        <v>73.69</v>
       </c>
       <c r="N53" t="n">
-        <v>35.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3605,14 +3595,14 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C54" t="n">
-        <v>4.972727272727273</v>
+        <v>6</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3625,33 +3615,33 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Brosay</t>
+          <t>Baldosa (IRE)</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="K54" t="n">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="L54" t="n">
-        <v>17.25</v>
+        <v>2.65</v>
       </c>
       <c r="M54" t="n">
-        <v>57.48</v>
+        <v>73.69</v>
       </c>
       <c r="N54" t="n">
-        <v>21.9</v>
+        <v>45.4</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3659,20 +3649,20 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C55" t="n">
-        <v>4.972727272727273</v>
+        <v>6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3685,46 +3675,54 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4</v>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Clarendon House</t>
+          <t>Thankfully Simmy</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K55" t="n">
-        <v>105</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
+        <v>64</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3.9</v>
+      </c>
       <c r="M55" t="n">
-        <v>57.48</v>
-      </c>
-      <c r="N55" t="inlineStr"/>
+        <v>73.69</v>
+      </c>
+      <c r="N55" t="n">
+        <v>49.4</v>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>7</v>
       </c>
       <c r="C56" t="n">
-        <v>12.06363636363636</v>
+        <v>6</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3740,47 +3738,51 @@
         <v>5</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Velvet Red (IRE)</t>
+          <t>Brave Traveller</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K56" t="n">
-        <v>67</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="L56" t="n">
+        <v>3.93</v>
+      </c>
       <c r="M56" t="n">
-        <v>158.52</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
+        <v>73.69</v>
+      </c>
+      <c r="N56" t="n">
+        <v>50.1</v>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>7</v>
       </c>
       <c r="C57" t="n">
-        <v>12.06363636363636</v>
+        <v>6</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3796,28 +3798,30 @@
         <v>5</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Solar Pass</t>
+          <t>Everydaysasaturday (IRE)</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="K57" t="n">
-        <v>70</v>
-      </c>
-      <c r="L57" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="L57" t="n">
+        <v>5.43</v>
+      </c>
       <c r="M57" t="n">
-        <v>158.52</v>
+        <v>73.69</v>
       </c>
       <c r="N57" t="n">
-        <v>60.2</v>
+        <v>39.1</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3831,14 +3835,14 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>7</v>
       </c>
       <c r="C58" t="n">
-        <v>12.06363636363636</v>
+        <v>6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3854,30 +3858,30 @@
         <v>5</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Lilly Lux (FR)</t>
+          <t>Peggy Boo</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="K58" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5</v>
+        <v>19.43</v>
       </c>
       <c r="M58" t="n">
-        <v>158.52</v>
+        <v>73.69</v>
       </c>
       <c r="N58" t="n">
-        <v>59.2</v>
+        <v>-11.5</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3891,74 +3895,70 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>8</v>
+      </c>
+      <c r="C59" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>6</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Jkr Cobbler (IRE)</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
         <v>7</v>
       </c>
-      <c r="C59" t="n">
-        <v>12.06363636363636</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>All Weather</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>5</v>
-      </c>
-      <c r="G59" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Hackney Diamonds</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>4</v>
-      </c>
       <c r="J59" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K59" t="n">
-        <v>60</v>
-      </c>
-      <c r="L59" t="n">
-        <v>3.25</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
-        <v>158.52</v>
-      </c>
-      <c r="N59" t="n">
-        <v>44.9</v>
-      </c>
+        <v>73.31</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>-1</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C60" t="n">
-        <v>12.06363636363636</v>
+        <v>6</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3971,54 +3971,50 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Little Miss India (IRE)</t>
+          <t>Tomorrow Day</t>
         </is>
       </c>
       <c r="I60" t="n">
         <v>5</v>
       </c>
       <c r="J60" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="K60" t="n">
-        <v>69</v>
-      </c>
-      <c r="L60" t="n">
-        <v>5</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>158.52</v>
-      </c>
-      <c r="N60" t="n">
-        <v>51.7</v>
-      </c>
+        <v>73.31</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C61" t="n">
-        <v>12.06363636363636</v>
+        <v>6</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4031,33 +4027,31 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Green Sky (IRE)</t>
+          <t>Pit Boss</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K61" t="n">
-        <v>69</v>
-      </c>
-      <c r="L61" t="n">
-        <v>8.25</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>158.52</v>
+        <v>73.31</v>
       </c>
       <c r="N61" t="n">
-        <v>44.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4065,20 +4059,20 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C62" t="n">
-        <v>12.06363636363636</v>
+        <v>6</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4091,33 +4085,33 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Late Claim (FR)</t>
+          <t>Andalprofit (IRE)</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="K62" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L62" t="n">
-        <v>13</v>
+        <v>0.15</v>
       </c>
       <c r="M62" t="n">
-        <v>158.52</v>
+        <v>73.31</v>
       </c>
       <c r="N62" t="n">
-        <v>17.6</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4125,20 +4119,20 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63" t="n">
-        <v>12.06363636363636</v>
+        <v>6</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4151,33 +4145,33 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G63" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Lady Justice</t>
+          <t>Instant Bond</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K63" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L63" t="n">
-        <v>15.75</v>
+        <v>2.9</v>
       </c>
       <c r="M63" t="n">
-        <v>158.52</v>
+        <v>73.31</v>
       </c>
       <c r="N63" t="n">
-        <v>17.5</v>
+        <v>54.2</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4191,14 +4185,14 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>8</v>
       </c>
       <c r="C64" t="n">
-        <v>7.063636363636363</v>
+        <v>6</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4211,31 +4205,33 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sea Suite (IRE)</t>
+          <t>Asadjumeirah</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J64" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K64" t="n">
-        <v>72</v>
-      </c>
-      <c r="L64" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="L64" t="n">
+        <v>4.15</v>
+      </c>
       <c r="M64" t="n">
-        <v>88.18000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="N64" t="n">
-        <v>66.7</v>
+        <v>44.3</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4249,14 +4245,14 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>8</v>
       </c>
       <c r="C65" t="n">
-        <v>7.063636363636363</v>
+        <v>6</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4269,33 +4265,33 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Ash Wednesday</t>
+          <t>Spun To Gold (USA)</t>
         </is>
       </c>
       <c r="I65" t="n">
         <v>5</v>
       </c>
       <c r="J65" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K65" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="L65" t="n">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="M65" t="n">
-        <v>88.18000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="N65" t="n">
-        <v>61.9</v>
+        <v>41.8</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4303,20 +4299,20 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>8</v>
       </c>
       <c r="C66" t="n">
-        <v>7.063636363636363</v>
+        <v>6</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4329,33 +4325,33 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Grabajabba</t>
+          <t>Nazca</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J66" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="K66" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="L66" t="n">
-        <v>1.65</v>
+        <v>7.65</v>
       </c>
       <c r="M66" t="n">
-        <v>88.18000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="N66" t="n">
-        <v>64.7</v>
+        <v>28.2</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4363,20 +4359,20 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>8</v>
       </c>
       <c r="C67" t="n">
-        <v>7.063636363636363</v>
+        <v>6</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4389,33 +4385,33 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Habrdi (IRE)</t>
+          <t>Tarlac (IRE)</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K67" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L67" t="n">
-        <v>1.75</v>
+        <v>11.4</v>
       </c>
       <c r="M67" t="n">
-        <v>88.18000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="N67" t="n">
-        <v>53.2</v>
+        <v>26.6</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4423,20 +4419,20 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SOUTHWELL</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>8</v>
       </c>
       <c r="C68" t="n">
-        <v>7.063636363636363</v>
+        <v>6</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4449,33 +4445,33 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>King Of York (IRE)</t>
+          <t>South Road (IRE)</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K68" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L68" t="n">
-        <v>3.75</v>
+        <v>13.65</v>
       </c>
       <c r="M68" t="n">
-        <v>88.18000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="N68" t="n">
-        <v>53.2</v>
+        <v>19.7</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4483,7 +4479,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4493,10 +4489,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>7.063636363636363</v>
+        <v>6.072727272727272</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4509,33 +4505,31 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G69" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Blazing Son</t>
+          <t>Mount Ruapehu (IRE)</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J69" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K69" t="n">
-        <v>74</v>
-      </c>
-      <c r="L69" t="n">
-        <v>3.78</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
-        <v>88.18000000000001</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="N69" t="n">
-        <v>57.3</v>
+        <v>60.3</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4543,7 +4537,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="70">
@@ -4553,10 +4547,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>7.063636363636363</v>
+        <v>6.072727272727272</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4569,33 +4563,33 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G70" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Chesneys Charm</t>
+          <t>Tuscan Point (IRE)</t>
         </is>
       </c>
       <c r="I70" t="n">
         <v>4</v>
       </c>
       <c r="J70" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K70" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L70" t="n">
-        <v>5.779999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="M70" t="n">
-        <v>88.18000000000001</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="N70" t="n">
-        <v>50.6</v>
+        <v>64.8</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4603,7 +4597,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4613,10 +4607,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>7.063636363636363</v>
+        <v>6.072727272727272</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4629,33 +4623,33 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G71" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Thurso</t>
+          <t>Moonhall Lass (IRE)</t>
         </is>
       </c>
       <c r="I71" t="n">
         <v>4</v>
       </c>
       <c r="J71" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="K71" t="n">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="L71" t="n">
-        <v>6.779999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="M71" t="n">
-        <v>88.18000000000001</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="N71" t="n">
-        <v>48.4</v>
+        <v>46.1</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4663,7 +4657,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="72">
@@ -4673,10 +4667,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>7.063636363636363</v>
+        <v>6.072727272727272</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4689,33 +4683,33 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G72" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Stoneywell</t>
+          <t>Bullington Bry</t>
         </is>
       </c>
       <c r="I72" t="n">
         <v>4</v>
       </c>
       <c r="J72" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K72" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="L72" t="n">
-        <v>7.279999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="M72" t="n">
-        <v>88.18000000000001</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="N72" t="n">
-        <v>44.7</v>
+        <v>57.3</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -4723,7 +4717,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4733,10 +4727,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>7.063636363636363</v>
+        <v>6.072727272727272</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4749,33 +4743,33 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Al Muqdad</t>
+          <t>Ardaddy</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K73" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="L73" t="n">
-        <v>7.779999999999999</v>
+        <v>2.05</v>
       </c>
       <c r="M73" t="n">
-        <v>88.18000000000001</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="N73" t="n">
-        <v>44.3</v>
+        <v>50.1</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -4793,10 +4787,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>7.063636363636363</v>
+        <v>6.072727272727272</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4809,33 +4803,33 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G74" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Great</t>
+          <t>Amerjeet</t>
         </is>
       </c>
       <c r="I74" t="n">
         <v>4</v>
       </c>
       <c r="J74" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K74" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="L74" t="n">
-        <v>14.28</v>
+        <v>2.08</v>
       </c>
       <c r="M74" t="n">
-        <v>88.18000000000001</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="N74" t="n">
-        <v>28.6</v>
+        <v>52.7</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -4843,7 +4837,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4853,56 +4847,4046 @@
         </is>
       </c>
       <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="n">
+        <v>6.072727272727272</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>6</v>
+      </c>
+      <c r="G75" t="n">
+        <v>7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Up The Monk</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>126</v>
+      </c>
+      <c r="K75" t="n">
+        <v>51</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="M75" t="n">
+        <v>75.43000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>6</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Mr Fustic (IRE)</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
         <v>8</v>
       </c>
-      <c r="C75" t="n">
+      <c r="J76" t="n">
+        <v>133</v>
+      </c>
+      <c r="K76" t="n">
+        <v>53</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="N76" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>6</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Volendam</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>4</v>
+      </c>
+      <c r="J77" t="n">
+        <v>133</v>
+      </c>
+      <c r="K77" t="n">
+        <v>53</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M77" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="N77" t="n">
+        <v>52</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>6</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Heretic (IRE)</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>7</v>
+      </c>
+      <c r="J78" t="n">
+        <v>135</v>
+      </c>
+      <c r="K78" t="n">
+        <v>55</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M78" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="N78" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>6</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>4</v>
+      </c>
+      <c r="J79" t="n">
+        <v>131</v>
+      </c>
+      <c r="K79" t="n">
+        <v>51</v>
+      </c>
+      <c r="L79" t="n">
+        <v>3</v>
+      </c>
+      <c r="M79" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="N79" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>6</v>
+      </c>
+      <c r="G80" t="n">
+        <v>5</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Trais Fluors</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>12</v>
+      </c>
+      <c r="J80" t="n">
+        <v>135</v>
+      </c>
+      <c r="K80" t="n">
+        <v>55</v>
+      </c>
+      <c r="L80" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="M80" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="N80" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>6</v>
+      </c>
+      <c r="G81" t="n">
+        <v>6</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Ribston Pippin (IRE)</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>4</v>
+      </c>
+      <c r="J81" t="n">
+        <v>135</v>
+      </c>
+      <c r="K81" t="n">
+        <v>55</v>
+      </c>
+      <c r="L81" t="n">
+        <v>9</v>
+      </c>
+      <c r="M81" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="N81" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>6</v>
+      </c>
+      <c r="G82" t="n">
+        <v>7</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Dinah Myte</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>4</v>
+      </c>
+      <c r="J82" t="n">
+        <v>132</v>
+      </c>
+      <c r="K82" t="n">
+        <v>52</v>
+      </c>
+      <c r="L82" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M82" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="N82" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>6</v>
+      </c>
+      <c r="G83" t="n">
+        <v>8</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Conquest Of Power</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>6</v>
+      </c>
+      <c r="J83" t="n">
+        <v>127</v>
+      </c>
+      <c r="K83" t="n">
+        <v>47</v>
+      </c>
+      <c r="L83" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="M83" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="N83" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>6</v>
+      </c>
+      <c r="G84" t="n">
+        <v>9</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Fifty Sent</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>7</v>
+      </c>
+      <c r="J84" t="n">
+        <v>135</v>
+      </c>
+      <c r="K84" t="n">
+        <v>55</v>
+      </c>
+      <c r="L84" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="M84" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="N84" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>2</v>
+      </c>
+      <c r="C85" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>6</v>
+      </c>
+      <c r="G85" t="n">
+        <v>10</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Create (IRE)</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>6</v>
+      </c>
+      <c r="J85" t="n">
+        <v>131</v>
+      </c>
+      <c r="K85" t="n">
+        <v>51</v>
+      </c>
+      <c r="L85" t="n">
+        <v>17</v>
+      </c>
+      <c r="M85" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="N85" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2</v>
+      </c>
+      <c r="C86" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>6</v>
+      </c>
+      <c r="G86" t="n">
+        <v>11</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Coverbridge</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>4</v>
+      </c>
+      <c r="J86" t="n">
+        <v>128</v>
+      </c>
+      <c r="K86" t="n">
+        <v>48</v>
+      </c>
+      <c r="L86" t="n">
+        <v>24</v>
+      </c>
+      <c r="M86" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="N86" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>4</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Timber Twelve</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>3</v>
+      </c>
+      <c r="J87" t="n">
+        <v>130</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="N87" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>3</v>
+      </c>
+      <c r="C88" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>4</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Clatford (IRE)</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>3</v>
+      </c>
+      <c r="J88" t="n">
+        <v>125</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M88" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="N88" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>3</v>
+      </c>
+      <c r="C89" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>4</v>
+      </c>
+      <c r="G89" t="n">
+        <v>3</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Saint Of The Sea</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" t="n">
+        <v>123</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M89" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="N89" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>3</v>
+      </c>
+      <c r="C90" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" t="n">
+        <v>4</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Flash Kozo (IRE)</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>3</v>
+      </c>
+      <c r="J90" t="n">
+        <v>125</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M90" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="N90" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>4</v>
+      </c>
+      <c r="G91" t="n">
+        <v>5</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Floating Market</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>3</v>
+      </c>
+      <c r="J91" t="n">
+        <v>120</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="M91" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="N91" t="n">
+        <v>39</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>4</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Cobalt Comet</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>3</v>
+      </c>
+      <c r="J92" t="n">
+        <v>123</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="M92" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="N92" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>4</v>
+      </c>
+      <c r="G93" t="n">
+        <v>7</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Love Fresh</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>3</v>
+      </c>
+      <c r="J93" t="n">
+        <v>118</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="M93" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="N93" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>3</v>
+      </c>
+      <c r="C94" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>4</v>
+      </c>
+      <c r="G94" t="n">
+        <v>8</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Luscious Lil</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>3</v>
+      </c>
+      <c r="J94" t="n">
+        <v>120</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M94" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="N94" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>3</v>
+      </c>
+      <c r="C95" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>4</v>
+      </c>
+      <c r="G95" t="n">
+        <v>9</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>August Spring</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>4</v>
+      </c>
+      <c r="J95" t="n">
+        <v>140</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="M95" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>4</v>
+      </c>
+      <c r="C96" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>4</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Welbury</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>125</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="N96" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>4</v>
+      </c>
+      <c r="C97" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>4</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Tommos Ginjaninja</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>3</v>
+      </c>
+      <c r="J97" t="n">
+        <v>125</v>
+      </c>
+      <c r="K97" t="n">
+        <v>67</v>
+      </c>
+      <c r="L97" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M97" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="N97" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>4</v>
+      </c>
+      <c r="C98" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>4</v>
+      </c>
+      <c r="G98" t="n">
+        <v>3</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Tough Date (IRE)</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>3</v>
+      </c>
+      <c r="J98" t="n">
+        <v>125</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M98" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="N98" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>4</v>
+      </c>
+      <c r="C99" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>4</v>
+      </c>
+      <c r="G99" t="n">
+        <v>4</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Portman Blue</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>4</v>
+      </c>
+      <c r="J99" t="n">
+        <v>142</v>
+      </c>
+      <c r="K99" t="n">
+        <v>72</v>
+      </c>
+      <c r="L99" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M99" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="N99" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>4</v>
+      </c>
+      <c r="C100" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>4</v>
+      </c>
+      <c r="G100" t="n">
+        <v>5</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Lorton Valley</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>3</v>
+      </c>
+      <c r="J100" t="n">
+        <v>125</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="M100" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="N100" t="n">
+        <v>19</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>4</v>
+      </c>
+      <c r="C101" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>4</v>
+      </c>
+      <c r="G101" t="n">
+        <v>6</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Filly Eilish (IRE)</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>3</v>
+      </c>
+      <c r="J101" t="n">
+        <v>118</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>11</v>
+      </c>
+      <c r="M101" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="N101" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>4</v>
+      </c>
+      <c r="C102" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>4</v>
+      </c>
+      <c r="G102" t="n">
+        <v>7</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Alembic</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>3</v>
+      </c>
+      <c r="J102" t="n">
+        <v>125</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>15</v>
+      </c>
+      <c r="M102" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="N102" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>4</v>
+      </c>
+      <c r="C103" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>4</v>
+      </c>
+      <c r="G103" t="n">
+        <v>8</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Rocklaw</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>3</v>
+      </c>
+      <c r="J103" t="n">
+        <v>118</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="M103" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="N103" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C104" t="n">
+        <v>8.059090909090909</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>4</v>
+      </c>
+      <c r="G104" t="n">
+        <v>9</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sweetstevie</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>4</v>
+      </c>
+      <c r="J104" t="n">
+        <v>142</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M104" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>5</v>
+      </c>
+      <c r="C105" t="n">
         <v>7.063636363636363</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>All Weather</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G75" t="n">
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>4</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Baandee</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>3</v>
+      </c>
+      <c r="J105" t="n">
+        <v>128</v>
+      </c>
+      <c r="K105" t="n">
+        <v>75</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="n">
+        <v>91.06</v>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>5</v>
+      </c>
+      <c r="C106" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>4</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Tenzi (IRE)</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>3</v>
+      </c>
+      <c r="J106" t="n">
+        <v>128</v>
+      </c>
+      <c r="K106" t="n">
+        <v>68</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>91.06</v>
+      </c>
+      <c r="N106" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>5</v>
+      </c>
+      <c r="C107" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>4</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Irish Incentive (IRE)</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>3</v>
+      </c>
+      <c r="J107" t="n">
+        <v>128</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M107" t="n">
+        <v>91.06</v>
+      </c>
+      <c r="N107" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>5</v>
+      </c>
+      <c r="C108" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>4</v>
+      </c>
+      <c r="G108" t="n">
+        <v>3</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Wadirumm (IRE)</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>3</v>
+      </c>
+      <c r="J108" t="n">
+        <v>126</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="M108" t="n">
+        <v>91.06</v>
+      </c>
+      <c r="N108" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>5</v>
+      </c>
+      <c r="C109" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>4</v>
+      </c>
+      <c r="G109" t="n">
+        <v>4</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Ndoto</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>3</v>
+      </c>
+      <c r="J109" t="n">
+        <v>128</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="M109" t="n">
+        <v>91.06</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>5</v>
+      </c>
+      <c r="C110" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>4</v>
+      </c>
+      <c r="G110" t="n">
+        <v>5</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Curtain Caller</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>3</v>
+      </c>
+      <c r="J110" t="n">
+        <v>126</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M110" t="n">
+        <v>91.06</v>
+      </c>
+      <c r="N110" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>6</v>
+      </c>
+      <c r="C111" t="n">
+        <v>4.972727272727273</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Fahrenheit Seven</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>5</v>
+      </c>
+      <c r="J111" t="n">
+        <v>129</v>
+      </c>
+      <c r="K111" t="n">
+        <v>99</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N111" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>6</v>
+      </c>
+      <c r="C112" t="n">
+        <v>4.972727272727273</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>2</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Clearpoint</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>6</v>
+      </c>
+      <c r="J112" t="n">
+        <v>129</v>
+      </c>
+      <c r="K112" t="n">
+        <v>99</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N112" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>6</v>
+      </c>
+      <c r="C113" t="n">
+        <v>4.972727272727273</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>2</v>
+      </c>
+      <c r="G113" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Against The Wind</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>4</v>
+      </c>
+      <c r="J113" t="n">
+        <v>131</v>
+      </c>
+      <c r="K113" t="n">
+        <v>101</v>
+      </c>
+      <c r="L113" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M113" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N113" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>6</v>
+      </c>
+      <c r="C114" t="n">
+        <v>4.972727272727273</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>2</v>
+      </c>
+      <c r="G114" t="n">
+        <v>4</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Rhythm N Hooves</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>6</v>
+      </c>
+      <c r="J114" t="n">
+        <v>120</v>
+      </c>
+      <c r="K114" t="n">
+        <v>90</v>
+      </c>
+      <c r="L114" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M114" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N114" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>6</v>
+      </c>
+      <c r="C115" t="n">
+        <v>4.972727272727273</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>2</v>
+      </c>
+      <c r="G115" t="n">
+        <v>5</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kylian (IRE)</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>5</v>
+      </c>
+      <c r="J115" t="n">
+        <v>132</v>
+      </c>
+      <c r="K115" t="n">
+        <v>102</v>
+      </c>
+      <c r="L115" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M115" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N115" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>6</v>
+      </c>
+      <c r="C116" t="n">
+        <v>4.972727272727273</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>2</v>
+      </c>
+      <c r="G116" t="n">
+        <v>6</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Gaeli (ITY)</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>5</v>
+      </c>
+      <c r="J116" t="n">
+        <v>132</v>
+      </c>
+      <c r="K116" t="n">
+        <v>102</v>
+      </c>
+      <c r="L116" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M116" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N116" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>6</v>
+      </c>
+      <c r="C117" t="n">
+        <v>4.972727272727273</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>2</v>
+      </c>
+      <c r="G117" t="n">
+        <v>7</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Miss Attitude</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>6</v>
+      </c>
+      <c r="J117" t="n">
+        <v>133</v>
+      </c>
+      <c r="K117" t="n">
+        <v>103</v>
+      </c>
+      <c r="L117" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M117" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N117" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>6</v>
+      </c>
+      <c r="C118" t="n">
+        <v>4.972727272727273</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>2</v>
+      </c>
+      <c r="G118" t="n">
+        <v>8</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Spartan Arrow (IRE)</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>6</v>
+      </c>
+      <c r="J118" t="n">
+        <v>133</v>
+      </c>
+      <c r="K118" t="n">
+        <v>103</v>
+      </c>
+      <c r="L118" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M118" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N118" t="n">
+        <v>77</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>6</v>
+      </c>
+      <c r="C119" t="n">
+        <v>4.972727272727273</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" t="n">
+        <v>9</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Ziggys Triton (IRE)</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>4</v>
+      </c>
+      <c r="J119" t="n">
+        <v>119</v>
+      </c>
+      <c r="K119" t="n">
+        <v>89</v>
+      </c>
+      <c r="L119" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="M119" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N119" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>6</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4.972727272727273</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>2</v>
+      </c>
+      <c r="G120" t="n">
+        <v>10</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Vintage Clarets</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>7</v>
+      </c>
+      <c r="J120" t="n">
+        <v>123</v>
+      </c>
+      <c r="K120" t="n">
+        <v>93</v>
+      </c>
+      <c r="L120" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="M120" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N120" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>6</v>
+      </c>
+      <c r="C121" t="n">
+        <v>4.972727272727273</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>2</v>
+      </c>
+      <c r="G121" t="n">
+        <v>11</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Brosay</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>4</v>
+      </c>
+      <c r="J121" t="n">
+        <v>127</v>
+      </c>
+      <c r="K121" t="n">
+        <v>97</v>
+      </c>
+      <c r="L121" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="M121" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N121" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>6</v>
+      </c>
+      <c r="C122" t="n">
+        <v>4.972727272727273</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>2</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Clarendon House</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>8</v>
+      </c>
+      <c r="J122" t="n">
+        <v>135</v>
+      </c>
+      <c r="K122" t="n">
+        <v>105</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>7</v>
+      </c>
+      <c r="C123" t="n">
+        <v>12.06363636363636</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>5</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Velvet Red (IRE)</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>4</v>
+      </c>
+      <c r="J123" t="n">
+        <v>134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>67</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>158.52</v>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>7</v>
+      </c>
+      <c r="C124" t="n">
+        <v>12.06363636363636</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>5</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Solar Pass</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>4</v>
+      </c>
+      <c r="J124" t="n">
+        <v>137</v>
+      </c>
+      <c r="K124" t="n">
+        <v>70</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>158.52</v>
+      </c>
+      <c r="N124" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>7</v>
+      </c>
+      <c r="C125" t="n">
+        <v>12.06363636363636</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>5</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Lilly Lux (FR)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>5</v>
+      </c>
+      <c r="J125" t="n">
+        <v>137</v>
+      </c>
+      <c r="K125" t="n">
+        <v>69</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M125" t="n">
+        <v>158.52</v>
+      </c>
+      <c r="N125" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>7</v>
+      </c>
+      <c r="C126" t="n">
+        <v>12.06363636363636</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>5</v>
+      </c>
+      <c r="G126" t="n">
+        <v>3</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Hackney Diamonds</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>4</v>
+      </c>
+      <c r="J126" t="n">
+        <v>127</v>
+      </c>
+      <c r="K126" t="n">
+        <v>60</v>
+      </c>
+      <c r="L126" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M126" t="n">
+        <v>158.52</v>
+      </c>
+      <c r="N126" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>7</v>
+      </c>
+      <c r="C127" t="n">
+        <v>12.06363636363636</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>5</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Little Miss India (IRE)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>5</v>
+      </c>
+      <c r="J127" t="n">
+        <v>137</v>
+      </c>
+      <c r="K127" t="n">
+        <v>69</v>
+      </c>
+      <c r="L127" t="n">
+        <v>5</v>
+      </c>
+      <c r="M127" t="n">
+        <v>158.52</v>
+      </c>
+      <c r="N127" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>7</v>
+      </c>
+      <c r="C128" t="n">
+        <v>12.06363636363636</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>5</v>
+      </c>
+      <c r="G128" t="n">
+        <v>5</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Green Sky (IRE)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>6</v>
+      </c>
+      <c r="J128" t="n">
+        <v>137</v>
+      </c>
+      <c r="K128" t="n">
+        <v>69</v>
+      </c>
+      <c r="L128" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="M128" t="n">
+        <v>158.52</v>
+      </c>
+      <c r="N128" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>7</v>
+      </c>
+      <c r="C129" t="n">
+        <v>12.06363636363636</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>5</v>
+      </c>
+      <c r="G129" t="n">
+        <v>6</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Late Claim (FR)</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>5</v>
+      </c>
+      <c r="J129" t="n">
+        <v>119</v>
+      </c>
+      <c r="K129" t="n">
+        <v>51</v>
+      </c>
+      <c r="L129" t="n">
+        <v>13</v>
+      </c>
+      <c r="M129" t="n">
+        <v>158.52</v>
+      </c>
+      <c r="N129" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>7</v>
+      </c>
+      <c r="C130" t="n">
+        <v>12.06363636363636</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>5</v>
+      </c>
+      <c r="G130" t="n">
+        <v>7</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Lady Justice</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>4</v>
+      </c>
+      <c r="J130" t="n">
+        <v>125</v>
+      </c>
+      <c r="K130" t="n">
+        <v>58</v>
+      </c>
+      <c r="L130" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="M130" t="n">
+        <v>158.52</v>
+      </c>
+      <c r="N130" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>8</v>
+      </c>
+      <c r="C131" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>5</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sea Suite (IRE)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>4</v>
+      </c>
+      <c r="J131" t="n">
+        <v>132</v>
+      </c>
+      <c r="K131" t="n">
+        <v>72</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="N131" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>8</v>
+      </c>
+      <c r="C132" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>5</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Ash Wednesday</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>5</v>
+      </c>
+      <c r="J132" t="n">
+        <v>132</v>
+      </c>
+      <c r="K132" t="n">
+        <v>72</v>
+      </c>
+      <c r="L132" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M132" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="N132" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>8</v>
+      </c>
+      <c r="C133" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>5</v>
+      </c>
+      <c r="G133" t="n">
+        <v>3</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Grabajabba</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>5</v>
+      </c>
+      <c r="J133" t="n">
+        <v>135</v>
+      </c>
+      <c r="K133" t="n">
+        <v>75</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M133" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="N133" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>8</v>
+      </c>
+      <c r="C134" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>4</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Habrdi (IRE)</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>5</v>
+      </c>
+      <c r="J134" t="n">
+        <v>124</v>
+      </c>
+      <c r="K134" t="n">
+        <v>64</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M134" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="N134" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>8</v>
+      </c>
+      <c r="C135" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>5</v>
+      </c>
+      <c r="G135" t="n">
+        <v>5</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>King Of York (IRE)</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>7</v>
+      </c>
+      <c r="J135" t="n">
+        <v>129</v>
+      </c>
+      <c r="K135" t="n">
+        <v>69</v>
+      </c>
+      <c r="L135" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="M135" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="N135" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>8</v>
+      </c>
+      <c r="C136" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>5</v>
+      </c>
+      <c r="G136" t="n">
+        <v>6</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Blazing Son</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>8</v>
+      </c>
+      <c r="J136" t="n">
+        <v>134</v>
+      </c>
+      <c r="K136" t="n">
+        <v>74</v>
+      </c>
+      <c r="L136" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="M136" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="N136" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>8</v>
+      </c>
+      <c r="C137" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>5</v>
+      </c>
+      <c r="G137" t="n">
+        <v>7</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Chesneys Charm</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>4</v>
+      </c>
+      <c r="J137" t="n">
+        <v>133</v>
+      </c>
+      <c r="K137" t="n">
+        <v>73</v>
+      </c>
+      <c r="L137" t="n">
+        <v>5.779999999999999</v>
+      </c>
+      <c r="M137" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="N137" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>8</v>
+      </c>
+      <c r="C138" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>5</v>
+      </c>
+      <c r="G138" t="n">
+        <v>8</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Thurso</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>4</v>
+      </c>
+      <c r="J138" t="n">
+        <v>133</v>
+      </c>
+      <c r="K138" t="n">
+        <v>73</v>
+      </c>
+      <c r="L138" t="n">
+        <v>6.779999999999999</v>
+      </c>
+      <c r="M138" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="N138" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>8</v>
+      </c>
+      <c r="C139" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>5</v>
+      </c>
+      <c r="G139" t="n">
+        <v>9</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Stoneywell</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>4</v>
+      </c>
+      <c r="J139" t="n">
+        <v>131</v>
+      </c>
+      <c r="K139" t="n">
+        <v>71</v>
+      </c>
+      <c r="L139" t="n">
+        <v>7.279999999999999</v>
+      </c>
+      <c r="M139" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="N139" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>8</v>
+      </c>
+      <c r="C140" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>5</v>
+      </c>
+      <c r="G140" t="n">
+        <v>10</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Al Muqdad</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>6</v>
+      </c>
+      <c r="J140" t="n">
+        <v>132</v>
+      </c>
+      <c r="K140" t="n">
+        <v>72</v>
+      </c>
+      <c r="L140" t="n">
+        <v>7.779999999999999</v>
+      </c>
+      <c r="M140" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="N140" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>8</v>
+      </c>
+      <c r="C141" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>5</v>
+      </c>
+      <c r="G141" t="n">
+        <v>11</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>4</v>
+      </c>
+      <c r="J141" t="n">
+        <v>134</v>
+      </c>
+      <c r="K141" t="n">
+        <v>74</v>
+      </c>
+      <c r="L141" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="M141" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="N141" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>SOUTHWELL</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>8</v>
+      </c>
+      <c r="C142" t="n">
+        <v>7.063636363636363</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>5</v>
+      </c>
+      <c r="G142" t="n">
         <v>12</v>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H142" t="inlineStr">
         <is>
           <t>Too Sweet</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>4</v>
-      </c>
-      <c r="J75" t="n">
+      <c r="I142" t="n">
+        <v>4</v>
+      </c>
+      <c r="J142" t="n">
         <v>130</v>
       </c>
-      <c r="K75" t="n">
+      <c r="K142" t="n">
         <v>70</v>
       </c>
-      <c r="L75" t="n">
+      <c r="L142" t="n">
         <v>19.28</v>
       </c>
-      <c r="M75" t="n">
+      <c r="M142" t="n">
         <v>88.18000000000001</v>
       </c>
-      <c r="N75" t="n">
+      <c r="N142" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P75" t="n">
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
         <v>0</v>
       </c>
     </row>
